--- a/artfynd/A 50982-2025 artfynd.xlsx
+++ b/artfynd/A 50982-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -897,6 +897,209 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129505635</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Västra Kolgården, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>589768</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6933014</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129505648</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80053</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Västra Kolgården, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>589731</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6933006</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50982-2025 artfynd.xlsx
+++ b/artfynd/A 50982-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>129505635</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>129505648</v>
       </c>
       <c r="B5" t="n">
-        <v>80053</v>
+        <v>80079</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 50982-2025 artfynd.xlsx
+++ b/artfynd/A 50982-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>129505635</v>
       </c>
       <c r="B4" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>129505648</v>
       </c>
       <c r="B5" t="n">
-        <v>80079</v>
+        <v>80084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 50982-2025 artfynd.xlsx
+++ b/artfynd/A 50982-2025 artfynd.xlsx
@@ -899,54 +899,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129505635</v>
+        <v>129505648</v>
       </c>
       <c r="B4" t="n">
-        <v>57735</v>
+        <v>80085</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589768</v>
+        <v>589731</v>
       </c>
       <c r="R4" t="n">
-        <v>6933014</v>
+        <v>6933006</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,45 +996,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129505648</v>
+        <v>129505635</v>
       </c>
       <c r="B5" t="n">
-        <v>80084</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589731</v>
+        <v>589768</v>
       </c>
       <c r="R5" t="n">
-        <v>6933006</v>
+        <v>6933014</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 50982-2025 artfynd.xlsx
+++ b/artfynd/A 50982-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>129505648</v>
       </c>
       <c r="B4" t="n">
-        <v>80085</v>
+        <v>80090</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50982-2025 artfynd.xlsx
+++ b/artfynd/A 50982-2025 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>129505635</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 50982-2025 artfynd.xlsx
+++ b/artfynd/A 50982-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124071664</v>
+        <v>129505648</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lunglav , Mpd</t>
+          <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589703</v>
+        <v>589731</v>
       </c>
       <c r="R2" t="n">
-        <v>6933013</v>
+        <v>6933006</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:54</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:54</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,62 +760,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124738463</v>
+        <v>124071156</v>
       </c>
       <c r="B3" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Näverbäcken, Mpd</t>
+          <t>Lunglav , Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>589686</v>
       </c>
       <c r="R3" t="n">
-        <v>6933032</v>
+        <v>6933010</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +837,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,45 +879,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129505648</v>
+        <v>124071407</v>
       </c>
       <c r="B4" t="n">
-        <v>80090</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Västra Kolgården, Mpd</t>
+          <t>Lunglav, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589731</v>
+        <v>589693</v>
       </c>
       <c r="R4" t="n">
-        <v>6933006</v>
+        <v>6933011</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,12 +944,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,22 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129505635</v>
+        <v>124071664</v>
       </c>
       <c r="B5" t="n">
-        <v>57741</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,43 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Västra Kolgården, Mpd</t>
+          <t>Lunglav , Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589768</v>
+        <v>589703</v>
       </c>
       <c r="R5" t="n">
-        <v>6933014</v>
+        <v>6933013</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,12 +1051,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1090,15 +1081,437 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>124735185</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Näverbäcken , Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>589665</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6933025</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129505689</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Västra Kolgården, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>589699</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6932982</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Joel Helker-Nygren</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Joel Helker-Nygren</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129505635</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Västra Kolgården, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>589768</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6933014</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>124738463</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Näverbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>589686</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6933032</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50982-2025 artfynd.xlsx
+++ b/artfynd/A 50982-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129505648</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124071156</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124071407</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124071664</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124735185</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1299,6 +1329,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129505689</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1405,6 +1440,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129505635</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1512,8 +1552,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124738463</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>